--- a/AAII_Financials/Quarterly/RHHBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RHHBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
   <si>
     <t>RHHBY</t>
   </si>
@@ -656,63 +656,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -746,8 +752,14 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -781,8 +793,14 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -816,8 +834,14 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -831,8 +855,10 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -866,8 +892,14 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -901,8 +933,14 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -936,8 +974,14 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -971,8 +1015,14 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -983,8 +1033,10 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1018,8 +1070,14 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1053,8 +1111,14 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1068,8 +1132,10 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1103,8 +1169,14 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1138,8 +1210,14 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1173,8 +1251,14 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1208,8 +1292,14 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1243,8 +1333,14 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1278,8 +1374,14 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1313,8 +1415,14 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1348,8 +1456,14 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1383,8 +1497,14 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1418,8 +1538,14 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1453,8 +1579,14 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1488,8 +1620,14 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1523,8 +1661,14 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1558,8 +1702,14 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1593,8 +1743,14 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1628,48 +1784,60 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1683,8 +1851,10 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1698,323 +1868,379 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6742600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>6792000</v>
+      </c>
+      <c r="F41" s="3">
         <v>7039500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>7000400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>9498500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8545700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>7697100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8257300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>5368400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>5347800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>6384300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>5878700</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5304500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>5343300</v>
+      </c>
+      <c r="F42" s="3">
         <v>12490100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>12420700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>5623200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>5059100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>11430400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>12262200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>4440200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>4423300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>6098100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>5615200</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16513600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>16634700</v>
+      </c>
+      <c r="F43" s="3">
         <v>17539600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>17442100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>15540400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>13981600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>14856900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>15938000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>13887200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>13834000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>15342100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>14127000</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10017300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>10090800</v>
+      </c>
+      <c r="F44" s="3">
         <v>9431900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>9379500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>9552600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>8594400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>8393500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>9004300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>8841500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>8807700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>9202400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>8473600</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5279700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5318400</v>
+      </c>
+      <c r="F45" s="3">
         <v>596500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>593200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>4677600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>4208400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>427100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>458100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>4886500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>4867800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1261200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1161300</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>43857700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>44179200</v>
+      </c>
+      <c r="F46" s="3">
         <v>48841700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>48570300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>44892400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>40389200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>44181100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>47396100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>37423800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>37280600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>39719300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>36573400</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3">
         <v>1015200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>1009600</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3">
         <v>946800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>1015700</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3">
         <v>937000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>862800</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28971500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>29183900</v>
+      </c>
+      <c r="F48" s="3">
         <v>28922400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>28761700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>28762200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>25877000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>26197900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>28104300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>26554600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>26453100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>27241500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>25083900</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>33526000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>33771800</v>
+      </c>
+      <c r="F49" s="3">
         <v>33814200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>33626400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>30595500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>27526400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>27785900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>29807900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>30385000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>30268800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>28760400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>26482500</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2048,8 +2274,14 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2083,43 +2315,55 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4387400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4419500</v>
+      </c>
+      <c r="F52" s="3">
         <v>3748000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>3727200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>4296600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>3865600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>3731000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>4002600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3738000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>3723700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>2574600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>2370700</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2153,43 +2397,55 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>121535900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>122426800</v>
+      </c>
+      <c r="F54" s="3">
         <v>126997900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>126292400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>119159300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>107206300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>112340800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>120515900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>106594700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>106187000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>107436500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>98927300</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2203,8 +2459,10 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2218,218 +2476,256 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6858900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6909200</v>
+      </c>
+      <c r="F57" s="3">
         <v>6654900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>6617900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>5673500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>5104400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>4802600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>5152100</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N57" s="3">
         <v>4493700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>4137800</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8147300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>8207000</v>
+      </c>
+      <c r="F58" s="3">
         <v>5704000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>5672300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>8257500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>7429200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>4725300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>5069200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>6700400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>6674800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>5651600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>5204000</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20695500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>20847300</v>
+      </c>
+      <c r="F59" s="3">
         <v>7484700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>7443100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>20748700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>18667300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>6167600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>6616500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>22900100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>22812500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>5760900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>5304600</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>35701700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>35963400</v>
+      </c>
+      <c r="F60" s="3">
         <v>35312400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>35116300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>34679600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>31200900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>29820800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>31990900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>29600500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>29487300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>29480100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>27145200</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>33075500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>33318000</v>
+      </c>
+      <c r="F61" s="3">
         <v>36161200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>35960300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>35290700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>31750700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>35420100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>37997700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>33556600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>33428300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>30984700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>28530700</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1466600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1477300</v>
+      </c>
+      <c r="F62" s="3">
         <v>1510800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1502400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1491300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1341700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1265800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1357900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1306500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1301500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1295600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1193000</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2463,8 +2759,14 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2498,8 +2800,14 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2533,43 +2841,55 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>76095300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>76653100</v>
+      </c>
+      <c r="F66" s="3">
         <v>79226900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>78786800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>77609100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>69824100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>72435900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>77707100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>70008900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>69741100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>67934600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>62554000</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2583,8 +2903,10 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2618,8 +2940,14 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2653,8 +2981,14 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2688,8 +3022,14 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2723,43 +3063,55 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>58849000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>59280400</v>
+      </c>
+      <c r="F72" s="3">
         <v>61589000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>61246800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>54041300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>48620400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>48381100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>51901800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>45838000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>45662700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>50289800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>46306700</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2793,8 +3145,14 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2828,8 +3186,14 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2863,43 +3227,55 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>40461600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>40758200</v>
+      </c>
+      <c r="F76" s="3">
         <v>42628200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>42391300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>36060300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>32443000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>35055900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>37607000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>32207900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>32084700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>34813400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>32056100</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2933,48 +3309,60 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3008,8 +3396,14 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3023,43 +3417,51 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>847500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>762500</v>
+      </c>
+      <c r="F83" s="3">
         <v>764200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>819800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>721100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>718400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>806900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>743000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>776100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>761000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>798700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>752500</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3093,8 +3495,14 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3128,8 +3536,14 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3163,8 +3577,14 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3198,8 +3618,14 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3233,43 +3659,55 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4724600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>4759300</v>
+      </c>
+      <c r="F89" s="3">
         <v>7410300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>7369100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>4463800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>4016100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>6720500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>7209600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>4403500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>4386700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>4867200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>4481700</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3283,43 +3721,51 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-971500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-978700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1304000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1296700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1056200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-950300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-995900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1068400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-959300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-955600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1188800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1094600</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3353,8 +3799,14 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3388,43 +3840,55 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1496900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>1507900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-6542700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-6506300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>1152400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>1036800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-4705500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-5047900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1594100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1588000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-6033400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-5555600</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3438,43 +3902,51 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>4828000</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>4863400</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>4860600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>4373000</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>4256600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>4240300</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3508,8 +3980,14 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3543,8 +4021,14 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3578,109 +4062,133 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6300100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-6346300</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2046200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-2034800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-5107000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-4594700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-755900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-810900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-3031900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-3020300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>2407200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>2216500</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-145200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-130700</v>
+      </c>
+      <c r="F101" s="3">
         <v>-72300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-77500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-84600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-84300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-257700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-237300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-220100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-215900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-141100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-133000</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-82900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-83500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1243500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1236500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>364000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>327500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1186900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1273200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-307100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-306000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>983300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>905400</v>
       </c>
     </row>
